--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,60 +794,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97176489</v>
+        <v>135312480</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A64828, Måsebo, Sm</t>
+          <t>Plöjan, Plöjan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587292</v>
+        <v>587057</v>
       </c>
       <c r="R3" t="n">
-        <v>6417181</v>
+        <v>6417353</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +883,592 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135312515</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587061</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6417342</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Förmodligen en kull</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135312305</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587055</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6417341</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97176489</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A64828, Måsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6417181</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135313094</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587014</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6417246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135312584</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587073</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6417327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,60 +804,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97176489</v>
+        <v>135312480</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>58265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A64828, Måsebo, Sm</t>
+          <t>Plöjan, Plöjan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587292</v>
+        <v>587057</v>
       </c>
       <c r="R3" t="n">
-        <v>6417181</v>
+        <v>6417353</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,25 +893,620 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135312480</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135312515</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587061</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6417342</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Förmodligen en kull</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135312515</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135312305</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587055</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6417341</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135312305</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97176489</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A64828, Måsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6417181</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/97176489</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135313094</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587014</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6417246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313094</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135312584</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587073</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6417327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135312584</t>
         </is>
       </c>
     </row>
@@ -931,6 +1514,11 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -1282,7 +1282,7 @@
         <v>135313094</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>135312584</v>
       </c>
       <c r="B8" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97176474</v>
+        <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A64828, Måsebo, Sm</t>
+          <t>A 31190, Måsebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587253</v>
+        <v>587359</v>
       </c>
       <c r="R2" t="n">
-        <v>6417204</v>
+        <v>6417089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,16 +781,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97176474</t>
+          <t>https://artportalen.se/Sighting/135946921</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135312480</v>
+        <v>97176474</v>
       </c>
       <c r="B3" t="n">
-        <v>58265</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,37 +798,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Plöjan, Plöjan, Sm</t>
+          <t>A64828, Måsebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587057</v>
+        <v>587253</v>
       </c>
       <c r="R3" t="n">
-        <v>6417353</v>
+        <v>6417204</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,33 +887,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135312480</t>
+          <t>https://artportalen.se/Sighting/97176474</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135312515</v>
+        <v>135312480</v>
       </c>
       <c r="B4" t="n">
-        <v>58139</v>
+        <v>58265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,43 +922,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Plöjan, Plöjan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587061</v>
+        <v>587057</v>
       </c>
       <c r="R4" t="n">
-        <v>6417342</v>
+        <v>6417353</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Förmodligen en kull</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,33 +1017,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135312515</t>
+          <t>https://artportalen.se/Sighting/135312480</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135312305</v>
+        <v>135312515</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103023</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,17 +1051,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Plöjan, Plöjan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587055</v>
+        <v>587061</v>
       </c>
       <c r="R5" t="n">
-        <v>6417341</v>
+        <v>6417342</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1112,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förmodligen en kull</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,66 +1143,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135312305</t>
+          <t>https://artportalen.se/Sighting/135312515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97176489</v>
+        <v>135312305</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A64828, Måsebo, Sm</t>
+          <t>Plöjan, Plöjan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587292</v>
+        <v>587055</v>
       </c>
       <c r="R6" t="n">
-        <v>6417181</v>
+        <v>6417341</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,22 +1214,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,34 +1238,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97176489</t>
+          <t>https://artportalen.se/Sighting/135312305</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135313094</v>
+        <v>97176489</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1291,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1317,19 +1299,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Plöjan, Plöjan, Sm</t>
+          <t>A64828, Måsebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587014</v>
+        <v>587292</v>
       </c>
       <c r="R7" t="n">
-        <v>6417246</v>
+        <v>6417181</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,22 +1338,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,71 +1362,81 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135313094</t>
+          <t>https://artportalen.se/Sighting/97176489</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135312584</v>
+        <v>135313094</v>
       </c>
       <c r="B8" t="n">
-        <v>101485</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Plöjan, Plöjan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587073</v>
+        <v>587014</v>
       </c>
       <c r="R8" t="n">
-        <v>6417327</v>
+        <v>6417246</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,6 +1500,118 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313094</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135312584</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Plöjan, Plöjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>587073</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6417327</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135312584</t>
         </is>
@@ -1519,6 +1626,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31190-2026 artfynd.xlsx
+++ b/artfynd/A 31190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946921</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
